--- a/Student_Githublinks.xlsx
+++ b/Student_Githublinks.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SN - B1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="728">
   <si>
     <t>S.No</t>
   </si>
@@ -2182,6 +2182,39 @@
   </si>
   <si>
     <t>https://github.com/sowmyapuranam/jfs-6th-sem</t>
+  </si>
+  <si>
+    <t>WebPages</t>
+  </si>
+  <si>
+    <t>MavenProjects</t>
+  </si>
+  <si>
+    <t>https://github.com/Vigneshgt/JFS-6th-sem</t>
+  </si>
+  <si>
+    <t>https://github.com/Avanija22/JFS_VISEM</t>
+  </si>
+  <si>
+    <t>https://github.com/harinietturouthu/JFS_VISEM</t>
+  </si>
+  <si>
+    <t>https://github.com/Sreeja-Rajoju/JFS_VI-SEM</t>
+  </si>
+  <si>
+    <t>https://github.com/Rohith053/JFS_VISEM</t>
+  </si>
+  <si>
+    <t>https://github.com/KadariUday/JFS_VISEM</t>
+  </si>
+  <si>
+    <t>https://github.com/GRahulVarma/JFS_6th-Sem</t>
+  </si>
+  <si>
+    <t>https://github.com/brithwik/JFS_VI-SEM</t>
+  </si>
+  <si>
+    <t>https://github.com/sagardeveloper-01/JFS_VISEM</t>
   </si>
 </sst>
 </file>
@@ -2250,7 +2283,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2286,12 +2319,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2346,6 +2390,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2627,7 +2680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.6328125" style="19" bestFit="1" customWidth="1"/>
@@ -2635,9 +2688,11 @@
     <col min="3" max="3" width="42.1796875" style="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.6328125" style="19" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.7265625" style="19" customWidth="1"/>
+    <col min="6" max="6" width="9.54296875" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2653,8 +2708,14 @@
       <c r="E1" s="3" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" s="22" t="s">
+        <v>717</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -2670,8 +2731,14 @@
       <c r="E2" s="20" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2" s="23">
+        <v>3</v>
+      </c>
+      <c r="G2" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -2687,8 +2754,14 @@
       <c r="E3" s="20" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3" s="23">
+        <v>3</v>
+      </c>
+      <c r="G3" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -2704,8 +2777,14 @@
       <c r="E4" s="20" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4" s="23">
+        <v>3</v>
+      </c>
+      <c r="G4" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>4</v>
       </c>
@@ -2721,8 +2800,14 @@
       <c r="E5" s="16" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5" s="23">
+        <v>3</v>
+      </c>
+      <c r="G5" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <v>5</v>
       </c>
@@ -2738,8 +2823,14 @@
       <c r="E6" s="20" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6" s="23">
+        <v>3</v>
+      </c>
+      <c r="G6" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>6</v>
       </c>
@@ -2755,8 +2846,14 @@
       <c r="E7" s="17" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F7" s="23">
+        <v>3</v>
+      </c>
+      <c r="G7" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -2772,8 +2869,10 @@
       <c r="E8" s="20" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>8</v>
       </c>
@@ -2789,8 +2888,10 @@
       <c r="E9" s="17" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <v>9</v>
       </c>
@@ -2806,8 +2907,10 @@
       <c r="E10" s="20" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>10</v>
       </c>
@@ -2823,8 +2926,10 @@
       <c r="E11" s="20" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
         <v>11</v>
       </c>
@@ -2840,8 +2945,14 @@
       <c r="E12" s="20" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F12" s="23">
+        <v>3</v>
+      </c>
+      <c r="G12" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>12</v>
       </c>
@@ -2857,8 +2968,14 @@
       <c r="E13" s="20" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F13" s="23">
+        <v>3</v>
+      </c>
+      <c r="G13" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <v>13</v>
       </c>
@@ -2874,8 +2991,14 @@
       <c r="E14" s="20" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F14" s="23">
+        <v>3</v>
+      </c>
+      <c r="G14" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>14</v>
       </c>
@@ -2891,8 +3014,14 @@
       <c r="E15" s="20" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F15" s="23">
+        <v>3</v>
+      </c>
+      <c r="G15" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="12">
         <v>15</v>
       </c>
@@ -2908,8 +3037,10 @@
       <c r="E16" s="20" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="14">
         <v>16</v>
       </c>
@@ -2923,8 +3054,10 @@
         <v>6</v>
       </c>
       <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
         <v>17</v>
       </c>
@@ -2938,8 +3071,10 @@
         <v>6</v>
       </c>
       <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="14">
         <v>18</v>
       </c>
@@ -2955,8 +3090,10 @@
       <c r="E19" s="20" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="12">
         <v>19</v>
       </c>
@@ -2972,8 +3109,14 @@
       <c r="E20" s="17" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20" s="23">
+        <v>3</v>
+      </c>
+      <c r="G20" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="14">
         <v>20</v>
       </c>
@@ -2989,8 +3132,10 @@
       <c r="E21" s="20" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="12">
         <v>21</v>
       </c>
@@ -3006,8 +3151,14 @@
       <c r="E22" s="17" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F22" s="23">
+        <v>3</v>
+      </c>
+      <c r="G22" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="14">
         <v>22</v>
       </c>
@@ -3023,8 +3174,14 @@
       <c r="E23" s="16" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F23" s="23">
+        <v>3</v>
+      </c>
+      <c r="G23" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="12">
         <v>23</v>
       </c>
@@ -3040,8 +3197,10 @@
       <c r="E24" s="17" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="14">
         <v>24</v>
       </c>
@@ -3057,8 +3216,14 @@
       <c r="E25" s="16" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F25" s="23">
+        <v>3</v>
+      </c>
+      <c r="G25" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="12">
         <v>25</v>
       </c>
@@ -3074,8 +3239,14 @@
       <c r="E26" s="17" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F26" s="23">
+        <v>3</v>
+      </c>
+      <c r="G26" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="14">
         <v>26</v>
       </c>
@@ -3089,8 +3260,10 @@
         <v>6</v>
       </c>
       <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="12">
         <v>27</v>
       </c>
@@ -3106,8 +3279,10 @@
       <c r="E28" s="20" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="14">
         <v>28</v>
       </c>
@@ -3121,8 +3296,10 @@
         <v>6</v>
       </c>
       <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="12">
         <v>29</v>
       </c>
@@ -3138,8 +3315,14 @@
       <c r="E30" s="20" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F30" s="23">
+        <v>3</v>
+      </c>
+      <c r="G30" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="14">
         <v>30</v>
       </c>
@@ -3155,8 +3338,14 @@
       <c r="E31" s="20" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F31" s="23">
+        <v>3</v>
+      </c>
+      <c r="G31" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="12">
         <v>31</v>
       </c>
@@ -3172,8 +3361,10 @@
       <c r="E32" s="17" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="14">
         <v>32</v>
       </c>
@@ -3187,8 +3378,10 @@
         <v>6</v>
       </c>
       <c r="E33" s="4"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="12">
         <v>33</v>
       </c>
@@ -3202,8 +3395,10 @@
         <v>6</v>
       </c>
       <c r="E34" s="4"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="14">
         <v>34</v>
       </c>
@@ -3219,8 +3414,14 @@
       <c r="E35" s="20" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F35" s="23">
+        <v>3</v>
+      </c>
+      <c r="G35" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="12">
         <v>35</v>
       </c>
@@ -3234,8 +3435,10 @@
         <v>6</v>
       </c>
       <c r="E36" s="4"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="14">
         <v>36</v>
       </c>
@@ -3249,8 +3452,10 @@
         <v>6</v>
       </c>
       <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="12">
         <v>37</v>
       </c>
@@ -3266,8 +3471,14 @@
       <c r="E38" s="20" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F38" s="23">
+        <v>3</v>
+      </c>
+      <c r="G38" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="14">
         <v>38</v>
       </c>
@@ -3283,8 +3494,10 @@
       <c r="E39" s="20" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="12">
         <v>39</v>
       </c>
@@ -3298,8 +3511,10 @@
         <v>6</v>
       </c>
       <c r="E40" s="4"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="14">
         <v>40</v>
       </c>
@@ -3315,8 +3530,14 @@
       <c r="E41" s="17" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F41" s="23">
+        <v>3</v>
+      </c>
+      <c r="G41" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="12">
         <v>41</v>
       </c>
@@ -3332,8 +3553,10 @@
       <c r="E42" s="16" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="14">
         <v>42</v>
       </c>
@@ -3349,8 +3572,14 @@
       <c r="E43" s="20" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F43" s="23">
+        <v>1</v>
+      </c>
+      <c r="G43" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="12">
         <v>43</v>
       </c>
@@ -3364,8 +3593,10 @@
         <v>6</v>
       </c>
       <c r="E44" s="4"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="14">
         <v>44</v>
       </c>
@@ -3379,8 +3610,10 @@
         <v>6</v>
       </c>
       <c r="E45" s="4"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="12">
         <v>45</v>
       </c>
@@ -3396,8 +3629,10 @@
       <c r="E46" s="16" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="14">
         <v>46</v>
       </c>
@@ -3413,8 +3648,10 @@
       <c r="E47" s="20" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="12">
         <v>47</v>
       </c>
@@ -3430,8 +3667,14 @@
       <c r="E48" s="17" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F48" s="23">
+        <v>2</v>
+      </c>
+      <c r="G48" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="14">
         <v>48</v>
       </c>
@@ -3447,8 +3690,10 @@
       <c r="E49" s="20" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="12">
         <v>49</v>
       </c>
@@ -3464,8 +3709,10 @@
       <c r="E50" s="16" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F50" s="23"/>
+      <c r="G50" s="23"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="14">
         <v>50</v>
       </c>
@@ -3479,8 +3726,10 @@
         <v>6</v>
       </c>
       <c r="E51" s="4"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F51" s="23"/>
+      <c r="G51" s="23"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="12">
         <v>51</v>
       </c>
@@ -3496,8 +3745,14 @@
       <c r="E52" s="16" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F52" s="23">
+        <v>3</v>
+      </c>
+      <c r="G52" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="14">
         <v>52</v>
       </c>
@@ -3513,8 +3768,14 @@
       <c r="E53" s="20" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F53" s="23">
+        <v>3</v>
+      </c>
+      <c r="G53" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="12">
         <v>53</v>
       </c>
@@ -3530,8 +3791,14 @@
       <c r="E54" s="16" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F54" s="23">
+        <v>3</v>
+      </c>
+      <c r="G54" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="14">
         <v>54</v>
       </c>
@@ -3547,8 +3814,10 @@
       <c r="E55" s="17" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="12">
         <v>55</v>
       </c>
@@ -3562,8 +3831,10 @@
         <v>6</v>
       </c>
       <c r="E56" s="4"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="14">
         <v>56</v>
       </c>
@@ -3579,8 +3850,14 @@
       <c r="E57" s="20" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F57" s="23">
+        <v>3</v>
+      </c>
+      <c r="G57" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="12">
         <v>57</v>
       </c>
@@ -3596,8 +3873,14 @@
       <c r="E58" s="16" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F58" s="23">
+        <v>3</v>
+      </c>
+      <c r="G58" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="14">
         <v>58</v>
       </c>
@@ -3613,8 +3896,10 @@
       <c r="E59" s="17" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="12">
         <v>59</v>
       </c>
@@ -3630,8 +3915,10 @@
       <c r="E60" s="17" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F60" s="23"/>
+      <c r="G60" s="23"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="14">
         <v>60</v>
       </c>
@@ -3645,8 +3932,10 @@
         <v>6</v>
       </c>
       <c r="E61" s="4"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F61" s="23"/>
+      <c r="G61" s="23"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="12">
         <v>61</v>
       </c>
@@ -3660,8 +3949,10 @@
         <v>6</v>
       </c>
       <c r="E62" s="4"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="14">
         <v>62</v>
       </c>
@@ -3677,8 +3968,14 @@
       <c r="E63" s="16" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F63" s="23">
+        <v>3</v>
+      </c>
+      <c r="G63" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="12">
         <v>63</v>
       </c>
@@ -3694,8 +3991,14 @@
       <c r="E64" s="17" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F64" s="23">
+        <v>3</v>
+      </c>
+      <c r="G64" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="14">
         <v>64</v>
       </c>
@@ -3711,8 +4014,14 @@
       <c r="E65" s="16" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F65" s="23">
+        <v>3</v>
+      </c>
+      <c r="G65" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="12">
         <v>65</v>
       </c>
@@ -3726,8 +4035,10 @@
         <v>6</v>
       </c>
       <c r="E66" s="4"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F66" s="23"/>
+      <c r="G66" s="23"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="14">
         <v>66</v>
       </c>
@@ -3743,8 +4054,14 @@
       <c r="E67" s="20" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F67" s="23">
+        <v>3</v>
+      </c>
+      <c r="G67" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="12">
         <v>67</v>
       </c>
@@ -3760,8 +4077,14 @@
       <c r="E68" s="20" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F68" s="23">
+        <v>3</v>
+      </c>
+      <c r="G68" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="14">
         <v>68</v>
       </c>
@@ -3777,8 +4100,10 @@
       <c r="E69" s="20" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F69" s="23"/>
+      <c r="G69" s="23"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="12">
         <v>69</v>
       </c>
@@ -3794,8 +4119,14 @@
       <c r="E70" s="16" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F70" s="23">
+        <v>3</v>
+      </c>
+      <c r="G70" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="14">
         <v>70</v>
       </c>
@@ -3811,8 +4142,14 @@
       <c r="E71" s="20" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F71" s="23">
+        <v>3</v>
+      </c>
+      <c r="G71" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="12">
         <v>71</v>
       </c>
@@ -3828,8 +4165,14 @@
       <c r="E72" s="17" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F72" s="23">
+        <v>3</v>
+      </c>
+      <c r="G72" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="14">
         <v>72</v>
       </c>
@@ -3845,8 +4188,14 @@
       <c r="E73" s="16" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F73" s="23">
+        <v>3</v>
+      </c>
+      <c r="G73" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="12">
         <v>73</v>
       </c>
@@ -3862,8 +4211,14 @@
       <c r="E74" s="16" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F74" s="23">
+        <v>1</v>
+      </c>
+      <c r="G74" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="14">
         <v>74</v>
       </c>
@@ -3879,8 +4234,14 @@
       <c r="E75" s="17" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F75" s="23">
+        <v>3</v>
+      </c>
+      <c r="G75" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="12">
         <v>75</v>
       </c>
@@ -3894,8 +4255,10 @@
         <v>6</v>
       </c>
       <c r="E76" s="4"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F76" s="23"/>
+      <c r="G76" s="23"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="14">
         <v>76</v>
       </c>
@@ -3909,8 +4272,10 @@
         <v>6</v>
       </c>
       <c r="E77" s="4"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F77" s="23"/>
+      <c r="G77" s="23"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="12">
         <v>77</v>
       </c>
@@ -3926,8 +4291,14 @@
       <c r="E78" s="16" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F78" s="23">
+        <v>3</v>
+      </c>
+      <c r="G78" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="14">
         <v>78</v>
       </c>
@@ -3943,8 +4314,14 @@
       <c r="E79" s="17" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F79" s="23">
+        <v>1</v>
+      </c>
+      <c r="G79" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="12">
         <v>79</v>
       </c>
@@ -3960,8 +4337,14 @@
       <c r="E80" s="16" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F80" s="23">
+        <v>3</v>
+      </c>
+      <c r="G80" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="14">
         <v>80</v>
       </c>
@@ -3975,8 +4358,10 @@
         <v>6</v>
       </c>
       <c r="E81" s="4"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F81" s="23"/>
+      <c r="G81" s="23"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="12">
         <v>81</v>
       </c>
@@ -3992,8 +4377,14 @@
       <c r="E82" s="17" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F82" s="23">
+        <v>3</v>
+      </c>
+      <c r="G82" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="14">
         <v>82</v>
       </c>
@@ -4007,8 +4398,10 @@
         <v>6</v>
       </c>
       <c r="E83" s="4"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F83" s="23"/>
+      <c r="G83" s="23"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="12">
         <v>83</v>
       </c>
@@ -4024,8 +4417,14 @@
       <c r="E84" s="20" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F84" s="23">
+        <v>3</v>
+      </c>
+      <c r="G84" s="23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="14">
         <v>84</v>
       </c>
@@ -4041,8 +4440,10 @@
       <c r="E85" s="16" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F85" s="23"/>
+      <c r="G85" s="23"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="12">
         <v>85</v>
       </c>
@@ -4058,8 +4459,10 @@
       <c r="E86" s="20" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F86" s="23"/>
+      <c r="G86" s="23"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="14">
         <v>86</v>
       </c>
@@ -4075,8 +4478,10 @@
       <c r="E87" s="20" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F87" s="23"/>
+      <c r="G87" s="23"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="12">
         <v>87</v>
       </c>
@@ -4090,8 +4495,10 @@
         <v>6</v>
       </c>
       <c r="E88" s="4"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F88" s="23"/>
+      <c r="G88" s="23"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="14">
         <v>88</v>
       </c>
@@ -4107,8 +4514,10 @@
       <c r="E89" s="20" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F89" s="23"/>
+      <c r="G89" s="23"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="12">
         <v>89</v>
       </c>
@@ -4124,9 +4533,14 @@
       <c r="E90" s="16" t="s">
         <v>551</v>
       </c>
+      <c r="F90" s="23">
+        <v>3</v>
+      </c>
+      <c r="G90" s="23">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E90"/>
   <hyperlinks>
     <hyperlink ref="E59" r:id="rId1"/>
     <hyperlink ref="E60" r:id="rId2"/>
@@ -4204,7 +4618,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E94"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.6328125" bestFit="1" customWidth="1"/>
@@ -4212,9 +4627,11 @@
     <col min="3" max="3" width="35.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.08984375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -4230,8 +4647,14 @@
       <c r="E1" s="3" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" s="22" t="s">
+        <v>717</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -4244,9 +4667,11 @@
       <c r="D2" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E2" s="21" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -4263,7 +4688,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -4278,7 +4703,7 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -4293,7 +4718,7 @@
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -4310,7 +4735,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -4327,7 +4752,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -4344,7 +4769,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -4359,7 +4784,7 @@
       </c>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -4376,7 +4801,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -4393,7 +4818,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -4408,7 +4833,7 @@
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -4425,7 +4850,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -4442,7 +4867,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -4459,7 +4884,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -4506,7 +4931,7 @@
       </c>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>18</v>
       </c>
@@ -4523,7 +4948,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -4540,7 +4965,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
         <v>20</v>
       </c>
@@ -4572,7 +4997,7 @@
       </c>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>22</v>
       </c>
@@ -4619,7 +5044,7 @@
       </c>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>25</v>
       </c>
@@ -4636,7 +5061,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
         <v>26</v>
       </c>
@@ -4653,7 +5078,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>27</v>
       </c>
@@ -4670,7 +5095,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>28</v>
       </c>
@@ -4702,7 +5127,7 @@
       </c>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
         <v>30</v>
       </c>
@@ -4719,7 +5144,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>31</v>
       </c>
@@ -4736,7 +5161,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9">
         <v>32</v>
       </c>
@@ -4768,7 +5193,7 @@
       </c>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
         <v>34</v>
       </c>
@@ -4785,7 +5210,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7">
         <v>35</v>
       </c>
@@ -4802,7 +5227,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9">
         <v>36</v>
       </c>
@@ -4819,7 +5244,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <v>37</v>
       </c>
@@ -4832,9 +5257,11 @@
       <c r="D38" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E38" s="4"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E38" s="21" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9">
         <v>38</v>
       </c>
@@ -4851,7 +5278,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>39</v>
       </c>
@@ -4868,7 +5295,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
         <v>40</v>
       </c>
@@ -4885,7 +5312,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="7">
         <v>41</v>
       </c>
@@ -4917,7 +5344,7 @@
       </c>
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>43</v>
       </c>
@@ -4949,7 +5376,7 @@
       </c>
       <c r="E45" s="4"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>45</v>
       </c>
@@ -4966,7 +5393,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9">
         <v>46</v>
       </c>
@@ -4979,9 +5406,11 @@
       <c r="D47" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E47" s="4"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E47" s="21" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>47</v>
       </c>
@@ -4998,7 +5427,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <v>48</v>
       </c>
@@ -5015,7 +5444,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>49</v>
       </c>
@@ -5028,9 +5457,11 @@
       <c r="D50" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E50" s="4"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E50" s="21" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9">
         <v>50</v>
       </c>
@@ -5062,7 +5493,7 @@
       </c>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9">
         <v>52</v>
       </c>
@@ -5079,7 +5510,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>53</v>
       </c>
@@ -5124,9 +5555,11 @@
       <c r="D56" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E56" s="4"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E56" s="21" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9">
         <v>56</v>
       </c>
@@ -5143,7 +5576,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>57</v>
       </c>
@@ -5156,9 +5589,11 @@
       <c r="D58" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E58" s="17"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E58" s="21" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9">
         <v>58</v>
       </c>
@@ -5175,7 +5610,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="7">
         <v>59</v>
       </c>
@@ -5192,7 +5627,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9">
         <v>60</v>
       </c>
@@ -5209,7 +5644,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="7">
         <v>61</v>
       </c>
@@ -5222,9 +5657,11 @@
       <c r="D62" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E62" s="4"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E62" s="21" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9">
         <v>62</v>
       </c>
@@ -5241,7 +5678,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="7">
         <v>63</v>
       </c>
@@ -5258,7 +5695,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9">
         <v>64</v>
       </c>
@@ -5275,7 +5712,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="7">
         <v>65</v>
       </c>
@@ -5292,7 +5729,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9">
         <v>66</v>
       </c>
@@ -5309,7 +5746,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="7">
         <v>67</v>
       </c>
@@ -5341,7 +5778,7 @@
       </c>
       <c r="E69" s="4"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>69</v>
       </c>
@@ -5358,7 +5795,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9">
         <v>70</v>
       </c>
@@ -5390,7 +5827,7 @@
       </c>
       <c r="E72" s="4"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9">
         <v>72</v>
       </c>
@@ -5403,7 +5840,9 @@
       <c r="D73" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E73" s="4"/>
+      <c r="E73" s="21" t="s">
+        <v>723</v>
+      </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="7">
@@ -5420,7 +5859,7 @@
       </c>
       <c r="E74" s="4"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="9">
         <v>74</v>
       </c>
@@ -5437,7 +5876,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="7">
         <v>75</v>
       </c>
@@ -5454,7 +5893,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="9">
         <v>76</v>
       </c>
@@ -5471,7 +5910,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="7">
         <v>77</v>
       </c>
@@ -5488,7 +5927,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9">
         <v>78</v>
       </c>
@@ -5505,7 +5944,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="7">
         <v>79</v>
       </c>
@@ -5522,7 +5961,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="9">
         <v>80</v>
       </c>
@@ -5539,7 +5978,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="7">
         <v>81</v>
       </c>
@@ -5556,7 +5995,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9">
         <v>82</v>
       </c>
@@ -5569,7 +6008,9 @@
       <c r="D83" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E83" s="4"/>
+      <c r="E83" s="21" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="7">
@@ -5586,7 +6027,7 @@
       </c>
       <c r="E84" s="4"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="9">
         <v>84</v>
       </c>
@@ -5603,7 +6044,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="7">
         <v>85</v>
       </c>
@@ -5620,7 +6061,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9">
         <v>86</v>
       </c>
@@ -5637,7 +6078,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="7">
         <v>87</v>
       </c>
@@ -5654,7 +6095,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="9">
         <v>88</v>
       </c>
@@ -5671,7 +6112,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="7">
         <v>89</v>
       </c>
@@ -5688,7 +6129,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9">
         <v>90</v>
       </c>
@@ -5705,7 +6146,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="7">
         <v>91</v>
       </c>
@@ -5722,7 +6163,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="9">
         <v>92</v>
       </c>
@@ -5739,7 +6180,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="7">
         <v>93</v>
       </c>
@@ -5757,7 +6198,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E94"/>
+  <autoFilter ref="A1:E94">
+    <filterColumn colId="4">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="E27" r:id="rId1"/>
     <hyperlink ref="E51" r:id="rId2" display="https://github.com/vedhanth1249/JFS_VISEM.git"/>
@@ -5824,15 +6269,24 @@
     <hyperlink ref="E81" r:id="rId63"/>
     <hyperlink ref="E66" r:id="rId64"/>
     <hyperlink ref="E53" r:id="rId65"/>
+    <hyperlink ref="E83" r:id="rId66"/>
+    <hyperlink ref="E58" r:id="rId67"/>
+    <hyperlink ref="E62" r:id="rId68"/>
+    <hyperlink ref="E47" r:id="rId69"/>
+    <hyperlink ref="E73" r:id="rId70"/>
+    <hyperlink ref="E50" r:id="rId71"/>
+    <hyperlink ref="E2" r:id="rId72"/>
+    <hyperlink ref="E38" r:id="rId73"/>
+    <hyperlink ref="E56" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId66"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.6328125" bestFit="1" customWidth="1"/>
@@ -5840,9 +6294,11 @@
     <col min="3" max="3" width="29.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="59.08984375" customWidth="1"/>
+    <col min="6" max="6" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -5858,8 +6314,14 @@
       <c r="E1" s="3" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" s="22" t="s">
+        <v>717</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -5874,7 +6336,7 @@
       </c>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -5891,7 +6353,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -5906,7 +6368,7 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>4</v>
       </c>
@@ -5921,7 +6383,7 @@
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <v>5</v>
       </c>
@@ -5938,7 +6400,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>6</v>
       </c>
@@ -5955,7 +6417,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -5972,7 +6434,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>8</v>
       </c>
@@ -5987,7 +6449,7 @@
       </c>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <v>9</v>
       </c>
@@ -6004,7 +6466,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>10</v>
       </c>
@@ -6019,7 +6481,7 @@
       </c>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
         <v>11</v>
       </c>
@@ -6034,7 +6496,7 @@
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>12</v>
       </c>
@@ -6051,7 +6513,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <v>13</v>
       </c>
@@ -6068,7 +6530,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>14</v>
       </c>
@@ -6083,7 +6545,7 @@
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="12">
         <v>15</v>
       </c>
